--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>[['Fundo', '1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%', True], ['CDI', '1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%', False], ['Alfa', '0,01%', '0,03%', '0,06%', '0,33%', '1,24%', '35,75%', False], ['%', '101%', '100%', '100%', '101%', '103%', '109%', False]]</t>
+          <t>[['Fundo', '1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%', True], ['CDI', '1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%', False], ['Alfa', '0,01%', '0,03%', '0,06%', '0,33%', '1,24%', '35,75%', False], ['%', '100,59%', '100,31%', '100,43%', '101,12%', '102,80%', '108,74%', False]]</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>O TIVIO BANKS apresentou rentabilidade de 1,10% no mês (101% do CDI), acumulando 9,36% no ano. A alocação em crédito era de 76%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI+0,26%, com duration média de 1,12 ano.</t>
+          <t>O TIVIO BANKS apresentou rentabilidade de 1,10% no mês (100,59% do CDI), acumulando 9,36% no ano. A alocação em crédito era de 76%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI+0,26%, com duration média de 1,12 ano.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>[['Fundo', '1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%', True], ['IMA-B 5', '1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%', False], ['Alfa', '−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%', False], ['%', '99%', '65%', '74%', '82%', '89%', '88%', False]]</t>
+          <t>[['Fundo', '1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%', True], ['IMA-B 5', '1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%', False], ['Alfa', '−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%', False], ['%', '99,01%', '65,17%', '74,23%', '81,63%', '89,08%', '88,06%', False]]</t>
         </is>
       </c>
     </row>
@@ -2121,17 +2121,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>R$ 1.698.520.740,05</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>R$ 1.793.381.077,96</t>
+          <t>100,43%</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>R$ 1.397.203.402,03</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>R$ 1.449.683.179,97</t>
+          <t>100,31%</t>
         </is>
       </c>
     </row>
@@ -2175,17 +2175,17 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'total': '76', 'top': [{'p': '76,5%', 'n': 'financeiro'}, {'p': '23,7%', 'n': 'caixa'}]}</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>{'total': '76', 'top': [{'p': '76%', 'n': 'financeiro'}]}</t>
+          <t>100,59%</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2202,17 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>R$ 1.698.520.740,05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>R$ 1.793.381.077,96</t>
         </is>
       </c>
     </row>
@@ -2229,17 +2229,17 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>R$ 1.397.203.402,03</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>R$ 1.449.683.179,97</t>
         </is>
       </c>
     </row>
@@ -2256,17 +2256,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '76', 'top': [{'p': '76,5%', 'n': 'financeiro'}, {'p': '23,7%', 'n': 'caixa'}]}</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Taxa global: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '76', 'top': [{'p': '76%', 'n': 'financeiro'}]}</t>
         </is>
       </c>
     </row>
@@ -2278,22 +2278,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>104%</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -2305,22 +2305,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>R$ 1.983.487.947,49</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>R$ 1.815.644.128,24</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -2332,22 +2332,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>R$ 2.522.009.705,73</t>
+          <t>Taxa de administração: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>R$ 2.491.331.200,61</t>
+          <t>Taxa global: 0,25% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2364,17 +2364,17 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'total': '69', 'top': [{'p': '52%', 'n': 'financeiro'}, {'p': '4%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'transporte e logística'}]}</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>{'total': '61', 'top': [{'p': '45%', 'n': 'financeiro'}, {'p': '5%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'FIDC'}]}</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -2391,17 +2391,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>R$ 1.983.487.947,49</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>R$ 1.815.644.128,24</t>
         </is>
       </c>
     </row>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>R$ 2.522.009.705,73</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>R$ 2.491.331.200,61</t>
         </is>
       </c>
     </row>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '69', 'top': [{'p': '52%', 'n': 'financeiro'}, {'p': '4%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'transporte e logística'}]}</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Taxa global: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>{'total': '61', 'top': [{'p': '45%', 'n': 'financeiro'}, {'p': '5%', 'n': 'energia elétrica'}, {'p': '2%', 'n': 'FIDC'}]}</t>
         </is>
       </c>
     </row>
@@ -2467,22 +2467,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>0,44</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>103%</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2494,22 +2494,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>113%</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -2521,22 +2521,22 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>R$ 161.593.743,98</t>
+          <t>Taxa de administração: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>R$ 156.046.891,63</t>
+          <t>Taxa global: 0,20% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2553,17 +2553,17 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>R$ 140.997.685,81</t>
+          <t>102%</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>R$ 146.843.921,67</t>
+          <t>103%</t>
         </is>
       </c>
     </row>
@@ -2580,17 +2580,17 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'total': '74', 'top': [{'p': '29%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+          <t>113%</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>{'total': '73', 'top': [{'p': '28%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
+          <t>102%</t>
         </is>
       </c>
     </row>
@@ -2607,17 +2607,17 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1,00</t>
+          <t>R$ 161.593.743,98</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>R$ 156.046.891,63</t>
         </is>
       </c>
     </row>
@@ -2634,17 +2634,17 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>R$ 140.997.685,81</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>R$ 146.843.921,67</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>{'total': '74', 'top': [{'p': '29%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>{'total': '73', 'top': [{'p': '28%', 'n': 'financeiro'}, {'p': '13%', 'n': 'FIDC'}, {'p': '7%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
     </row>
@@ -2688,17 +2688,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,45% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>1,00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Taxa global: 0,50% a.a. Taxa de performance: 20% do que exceder 102,5% do CDI. Aplicação: D+0 · Resgate: D+0.</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -2710,22 +2710,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>113%</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>102%</t>
+          <t>1,80</t>
         </is>
       </c>
     </row>
@@ -2737,22 +2737,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>R$ 143.232.764,20</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>R$ 126.168.780,56</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2764,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>R$ 155.004.649,74</t>
+          <t>Taxa de administração: 0,45% a.a. Taxa de performance: não há. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>R$ 158.893.390,74</t>
+          <t>Taxa global: 0,50% a.a. Taxa de performance: 20% do que exceder 102,5% do CDI. Aplicação: D+0 · Resgate: D+0.</t>
         </is>
       </c>
     </row>
@@ -2796,17 +2796,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'total': '84', 'top': [{'p': '33%', 'n': 'financeiro'}, {'p': '15%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+          <t>113%</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>{'total': '80', 'top': [{'p': '31%', 'n': 'financeiro'}, {'p': '14%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
+          <t>102%</t>
         </is>
       </c>
     </row>
@@ -2823,17 +2823,17 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>R$ 143.232.764,20</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>R$ 126.168.780,56</t>
         </is>
       </c>
     </row>
@@ -2850,17 +2850,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>R$ 155.004.649,74</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>R$ 158.893.390,74</t>
         </is>
       </c>
     </row>
@@ -2877,17 +2877,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>{'total': '84', 'top': [{'p': '33%', 'n': 'financeiro'}, {'p': '15%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>{'total': '80', 'top': [{'p': '31%', 'n': 'financeiro'}, {'p': '14%', 'n': 'FIDC'}, {'p': '8%', 'n': 'energia elétrica'}]}</t>
         </is>
       </c>
     </row>
@@ -2904,17 +2904,17 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,63% a.a. Taxa de performance: 20% do que exceder o CDI. Resgate: D+30.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Taxa global: 0,625% a.a. Taxa de performance: 20% do que exceder 100% do CDI. Resgate: D+30.</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -2926,22 +2926,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -2953,22 +2953,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>*Alfa: -2,75%</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>*Alfa: −3,44%</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -2980,22 +2980,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>7,80%</t>
+          <t>Taxa de administração: 0,63% a.a. Taxa de performance: 20% do que exceder o CDI. Resgate: D+30.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>Taxa global: 0,625% a.a. Taxa de performance: 20% do que exceder 100% do CDI. Resgate: D+30.</t>
         </is>
       </c>
     </row>
@@ -3012,17 +3012,17 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>a2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>*Alfa: -3,14%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>*Alfa: −3,20%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -3039,17 +3039,17 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>a1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>*Alfa: -2,75%</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>*Alfa: −3,44%</t>
         </is>
       </c>
     </row>
@@ -3066,17 +3066,17 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>*Alfa: -0,14%</t>
+          <t>7,80%</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>*Alfa: −0,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>a2</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>R$ 42.983.282,75</t>
+          <t>*Alfa: -3,14%</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>R$ 42.694.019,75</t>
+          <t>*Alfa: −3,20%</t>
         </is>
       </c>
     </row>
@@ -3120,17 +3120,17 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>R$ 52.049.593,91</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>R$ 49.421.174,50</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3147,17 +3147,17 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>alloc</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'total': '95', 'top': [{'p': '55%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+          <t>*Alfa: -0,14%</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>{'total': '97', 'top': [{'p': '56%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
+          <t>*Alfa: −0,01%</t>
         </is>
       </c>
     </row>
@@ -3174,17 +3174,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>8,63</t>
+          <t>R$ 42.983.282,75</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>8,23</t>
+          <t>R$ 42.694.019,75</t>
         </is>
       </c>
     </row>
@@ -3201,17 +3201,17 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>R$ 52.049.593,91</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>R$ 49.421.174,50</t>
         </is>
       </c>
     </row>
@@ -3228,17 +3228,17 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>taxas</t>
+          <t>alloc</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Taxa de administração: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+          <t>{'total': '95', 'top': [{'p': '55%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Taxa global: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
+          <t>{'total': '97', 'top': [{'p': '56%', 'n': 'energia elétrica'}, {'p': '15%', 'n': 'transporte e logística'}, {'p': '7%', 'n': 'saneamento'}]}</t>
         </is>
       </c>
     </row>
@@ -3250,22 +3250,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>8,63</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>8,23</t>
         </is>
       </c>
     </row>
@@ -3277,22 +3277,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -3304,22 +3304,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>taxas</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>Taxa de administração: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>Taxa global: 0,75% a.a. Taxa de performance: não há. Resgate: D+31. Rentabilidade isenta de IR para pessoa física.</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>JULHO DE 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AGOSTO DE 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3395,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>const ATUAL=6;</t>
+          <t>JULHO DE 2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>const ATUAL=7;</t>
+          <t>AGOSTO DE 2026</t>
         </is>
       </c>
     </row>
@@ -3444,98 +3444,98 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>103%</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>101%</t>
+          <t>const ATUAL=6;</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>const ATUAL=7;</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>101%</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -3552,17 +3552,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>R$ 352,4 mi</t>
+          <t>103%</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>R$ 350,1 mi</t>
+          <t>91%</t>
         </is>
       </c>
     </row>
@@ -3574,17 +3574,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>104%</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -3601,22 +3601,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>106%</t>
+          <t>101%</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>105%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3628,22 +3628,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>109%</t>
+          <t>R$ 352,4 mi</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>107%</t>
+          <t>R$ 350,1 mi</t>
         </is>
       </c>
     </row>
@@ -3660,17 +3660,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>R$ 33,2 mi</t>
+          <t>104%</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>R$ 35,7 mi</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -3682,22 +3682,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>0,00% a.a. (vértice tx zero)</t>
+          <t>106%</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0,15% a.a.</t>
+          <t>105%</t>
         </is>
       </c>
     </row>
@@ -3709,22 +3709,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>109%</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>107%</t>
         </is>
       </c>
     </row>
@@ -3736,22 +3736,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>R$ 33,2 mi</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>R$ 35,7 mi</t>
         </is>
       </c>
     </row>
@@ -3768,17 +3768,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>R$ 374,3 mi</t>
+          <t>0,00% a.a. (vértice tx zero)</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>R$ 353,7 mi</t>
+          <t>0,15% a.a.</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>370%</t>
+          <t>99%</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -3844,22 +3844,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>R$ 374,3 mi</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>R$ 353,7 mi</t>
         </is>
       </c>
     </row>
@@ -3876,17 +3876,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>R$ 95,0 mi</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>R$ 91,4 mi</t>
+          <t>370%</t>
         </is>
       </c>
     </row>
@@ -3898,22 +3898,22 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>33%</t>
         </is>
       </c>
     </row>
@@ -3925,22 +3925,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>a1</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>*Alfa: −3,03%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>*Alfa: 0,21%</t>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -3952,22 +3952,22 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>−5,35%</t>
+          <t>R$ 95,0 mi</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>R$ 91,4 mi</t>
         </is>
       </c>
     </row>
@@ -3984,17 +3984,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>a2</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>*Alfa: −1,59%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>*Alfa: 0,45%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4011,17 +4011,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>a1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>*Alfa: −3,03%</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>*Alfa: 0,21%</t>
         </is>
       </c>
     </row>
@@ -4038,17 +4038,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>a3</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>*Alfa: −6,22%</t>
+          <t>−5,35%</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>*Alfa: −1,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -4065,17 +4065,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>a2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>R$ 100,8 mi</t>
+          <t>*Alfa: −1,59%</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>R$ 77,4 mi</t>
+          <t>*Alfa: 0,45%</t>
         </is>
       </c>
     </row>
@@ -4087,22 +4087,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20% do que exceder o CDI</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>20% do que exceder 100% do CDI</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -4114,22 +4114,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>*Alfa: −6,22%</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>*Alfa: −1,01%</t>
         </is>
       </c>
     </row>
@@ -4141,22 +4141,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>v2</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>R$ 100,8 mi</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>R$ 77,4 mi</t>
         </is>
       </c>
     </row>
@@ -4173,17 +4173,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>v3</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>20% do que exceder o CDI</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>20% do que exceder 100% do CDI</t>
         </is>
       </c>
     </row>
@@ -4200,17 +4200,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>R$ 102,7 mi</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>R$ 100,4 mi</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -4222,22 +4222,22 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>76%</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>v3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>R$ 662,8 mi</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>R$ 650,1 mi</t>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -4276,22 +4276,22 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>R$ 102,7 mi</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>R$ 100,4 mi</t>
         </is>
       </c>
     </row>
@@ -4303,22 +4303,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>prevlowvol</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>92%</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>95%</t>
         </is>
       </c>
     </row>
@@ -4330,22 +4330,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>prevlowvol</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>R$ 662,8 mi</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>R$ 650,1 mi</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>JULHO DE 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AGOSTO DE 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4421,12 +4421,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>const ATUAL=6;</t>
+          <t>JULHO DE 2026</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>const ATUAL=7;</t>
+          <t>AGOSTO DE 2026</t>
         </is>
       </c>
     </row>
@@ -4470,98 +4470,98 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>mercado</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>R$ 1.698.520.740,05</t>
+          <t>const ATUAL=6;</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>R$ 1.793.381.077,96</t>
+          <t>const ATUAL=7;</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>R$ 1.397.203.402,03</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>R$ 1.449.683.179,97</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -4573,22 +4573,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>mercado</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>MARKET</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'pct': ['101%', '100%', '100%']}</t>
+          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['101%', '100%', '100%', '101%', '103%', '109%']}</t>
+          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
         </is>
       </c>
     </row>
@@ -4605,17 +4605,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
+          <t>R$ 1.698.520.740,05</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
+          <t>R$ 1.793.381.077,96</t>
         </is>
       </c>
     </row>
@@ -4632,17 +4632,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
+          <t>R$ 1.397.203.402,03</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
+          <t>R$ 1.449.683.179,97</t>
         </is>
       </c>
     </row>
@@ -4659,17 +4659,17 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>{'pct': ['101%', '100%', '100%']}</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
+          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['100,59%', '100,31%', '100,43%', '101,12%', '102,80%', '108,74%'], 'alfa': ['0,01%', '0,03%', '0,06%', '0,33%', '1,24%', '35,75%']}</t>
         </is>
       </c>
     </row>
@@ -4686,17 +4686,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4713,17 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
         </is>
       </c>
     </row>
@@ -4740,17 +4740,17 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
         </is>
       </c>
     </row>
@@ -4767,17 +4767,17 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[12.0, 12.0, 'CDI']</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>[14.7, 14.63, 'CDI']</t>
+          <t>0,25%</t>
         </is>
       </c>
     </row>
@@ -4794,17 +4794,17 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
+          <t>1,05</t>
         </is>
       </c>
     </row>
@@ -4816,22 +4816,22 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>R$ 1.983.487.947,49</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>R$ 1.815.644.128,24</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -4843,22 +4843,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>R$ 2.522.009.705,73</t>
+          <t>[12.0, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>R$ 2.491.331.200,61</t>
+          <t>[14.7, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -4870,22 +4870,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'pct': ['104%', '100%', '100%']}</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%']}</t>
+          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
         </is>
       </c>
     </row>
@@ -4902,17 +4902,17 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
+          <t>R$ 1.983.487.947,49</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
+          <t>R$ 1.815.644.128,24</t>
         </is>
       </c>
     </row>
@@ -4929,17 +4929,17 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
+          <t>R$ 2.522.009.705,73</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
+          <t>R$ 2.491.331.200,61</t>
         </is>
       </c>
     </row>
@@ -4956,17 +4956,17 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>{'pct': ['104%', '100%', '100%']}</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
+          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%'], 'alfa': ['−0,01%', '−0,02%', '0,01%', '0,44%', '3,43%', '71,57%']}</t>
         </is>
       </c>
     </row>
@@ -4983,17 +4983,17 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
         </is>
       </c>
     </row>
@@ -5010,17 +5010,17 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1,20</t>
+          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
         </is>
       </c>
     </row>
@@ -5037,17 +5037,17 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5064,17 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[12.48, 12.0, 'CDI']</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>[14.64, 14.63, 'CDI']</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5091,17 +5091,17 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>1,20</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -5113,22 +5113,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>0,45% a.a.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>0,50% a.a.</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5140,22 +5140,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Não há</t>
+          <t>[12.48, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>20% do que exceder 102,5% do CDI</t>
+          <t>[14.64, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5167,22 +5167,22 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>R$ 161.593.743,98</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>R$ 156.046.891,63</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5199,17 +5199,17 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>R$ 140.997.685,81</t>
+          <t>0,45% a.a.</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>R$ 146.843.921,67</t>
+          <t>0,50% a.a.</t>
         </is>
       </c>
     </row>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>{'pct': ['113%', '102%', '102%']}</t>
+          <t>Não há</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%']}</t>
+          <t>20% do que exceder 102,5% do CDI</t>
         </is>
       </c>
     </row>
@@ -5253,17 +5253,17 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
+          <t>R$ 161.593.743,98</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
+          <t>R$ 156.046.891,63</t>
         </is>
       </c>
     </row>
@@ -5280,17 +5280,17 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
+          <t>R$ 140.997.685,81</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
+          <t>R$ 146.843.921,67</t>
         </is>
       </c>
     </row>
@@ -5307,17 +5307,17 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>{'pct': ['113%', '102%', '102%']}</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
+          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%'], 'alfa': ['0,02%', '0,20%', '0,36%', '1,43%', '7,05%', '236,24%']}</t>
         </is>
       </c>
     </row>
@@ -5334,17 +5334,17 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>1,00%</t>
+          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
         </is>
       </c>
     </row>
@@ -5361,17 +5361,17 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>1,80</t>
+          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
         </is>
       </c>
     </row>
@@ -5388,17 +5388,17 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
         </is>
       </c>
     </row>
@@ -5415,17 +5415,17 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>1,00%</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5442,17 +5442,17 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[12.24, 12.0, 'CDI']</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>[15.0, 14.63, 'CDI']</t>
+          <t>1,80</t>
         </is>
       </c>
     </row>
@@ -5469,17 +5469,17 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -5491,22 +5491,22 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>adm</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>0,63% a.a.</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0,625% a.a.</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5518,22 +5518,22 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>perf</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>20% do que exceder o CDI</t>
+          <t>[12.24, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>20% do que exceder 100% do CDI</t>
+          <t>[15.0, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>inst30</t>
+          <t>inst15</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>R$ 143.232.764,20</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>R$ 126.168.780,56</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5577,17 +5577,17 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>adm</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>R$ 155.004.649,74</t>
+          <t>0,63% a.a.</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>R$ 158.893.390,74</t>
+          <t>0,625% a.a.</t>
         </is>
       </c>
     </row>
@@ -5604,17 +5604,17 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>perf</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>{'pct': ['113%', '101%', '101%']}</t>
+          <t>20% do que exceder o CDI</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%']}</t>
+          <t>20% do que exceder 100% do CDI</t>
         </is>
       </c>
     </row>
@@ -5631,17 +5631,17 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
+          <t>R$ 143.232.764,20</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
+          <t>R$ 126.168.780,56</t>
         </is>
       </c>
     </row>
@@ -5658,17 +5658,17 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
+          <t>R$ 155.004.649,74</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
+          <t>R$ 158.893.390,74</t>
         </is>
       </c>
     </row>
@@ -5685,17 +5685,17 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>{'pct': ['113%', '101%', '101%']}</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
+          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%'], 'alfa': ['0,03%', '0,12%', '0,11%', '−', '−', '0,21%']}</t>
         </is>
       </c>
     </row>
@@ -5712,17 +5712,17 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
         </is>
       </c>
     </row>
@@ -5739,17 +5739,17 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
         </is>
       </c>
     </row>
@@ -5766,17 +5766,17 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>anos</t>
+          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ano</t>
+          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
         </is>
       </c>
     </row>
@@ -5793,17 +5793,17 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5820,17 +5820,17 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[12.12, 12.0, 'CDI']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>[14.75, 14.63, 'CDI']</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -5847,17 +5847,17 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
+          <t>anos</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
+          <t>ano</t>
         </is>
       </c>
     </row>
@@ -5869,22 +5869,22 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>R$ 42.983.282,75</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>R$ 42.694.019,75</t>
+          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
         </is>
       </c>
     </row>
@@ -5896,22 +5896,22 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>R$ 52.049.593,91</t>
+          <t>[12.12, 12.0, 'CDI']</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>R$ 49.421.174,50</t>
+          <t>[14.75, 14.63, 'CDI']</t>
         </is>
       </c>
     </row>
@@ -5923,22 +5923,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>inst30</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
+          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
+          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
         </is>
       </c>
     </row>
@@ -5955,17 +5955,17 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>pl</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
+          <t>R$ 42.983.282,75</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
+          <t>R$ 42.694.019,75</t>
         </is>
       </c>
     </row>
@@ -5982,17 +5982,17 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>plm</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
+          <t>R$ 52.049.593,91</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
+          <t>R$ 49.421.174,50</t>
         </is>
       </c>
     </row>
@@ -6009,17 +6009,17 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>perfrows</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
+          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
+          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
         </is>
       </c>
     </row>
@@ -6036,17 +6036,17 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>emissores</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
         </is>
       </c>
     </row>
@@ -6063,17 +6063,17 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>val</t>
+          <t>setores</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>4,00</t>
+          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>hist12</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
+          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
         </is>
       </c>
     </row>
@@ -6117,17 +6117,17 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>histEnd</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>[12.94, 15.69, 'IMA-B 5']</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>[9.78, 13.28, 'IMA-B 5']</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -6144,17 +6144,17 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>comentario</t>
+          <t>val</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
+          <t>4,00</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
+          <t>3,98</t>
         </is>
       </c>
     </row>
@@ -6166,22 +6166,22 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>hist12</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>31/07/2026</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
         </is>
       </c>
     </row>
@@ -6193,22 +6193,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>histEnd</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Julho de 2026</t>
+          <t>[12.94, 15.69, 'IMA-B 5']</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Agosto de 2026</t>
+          <t>[9.78, 13.28, 'IMA-B 5']</t>
         </is>
       </c>
     </row>
@@ -6220,22 +6220,22 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>comentario</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>julho de 2026</t>
+          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>agosto de 2026</t>
+          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6257,12 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>-jul26</t>
+          <t>Julho de 2026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>-ago26</t>
+          <t>Agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>julho/2026</t>
+          <t>julho de 2026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>agosto/2026</t>
+          <t>agosto de 2026</t>
         </is>
       </c>
     </row>
@@ -6338,12 +6338,12 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>const A=6;const track</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>const A=7;const track</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -6360,98 +6360,98 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>libs de exportação</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>CDN</t>
+          <t>-jul26</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
+          <t>-ago26</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>s1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>julho/2026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>agosto/2026</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>data</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>const A=6;const track</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>const A=7;const track</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>tivio-relatorio-gestao-credito-privado.html</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>s8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>libs de exportação</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Julho 2026</t>
+          <t>CDN</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>4 referências → vendor/ local (CDN como reserva)</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>r1</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6490,7 +6490,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>e1</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6517,22 +6517,22 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>r1</t>
+          <t>s8</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Relatórios de Gestão · Crédito Privado</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Gerador de Relatório de Gestão · Crédito Privado</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -6549,17 +6549,17 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -6571,22 +6571,22 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>e1</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Relatório de Gestão · Incentivado CDI 30</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Gerador de Relatório de Gestão · Incentivado CDI 30</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -6598,22 +6598,22 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>r2</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+          <t>Relatórios de Gestão · Crédito Privado</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+          <t>Gerador de Relatório de Gestão · Crédito Privado</t>
         </is>
       </c>
     </row>
@@ -6625,22 +6625,22 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>r1</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>cards de relatório</t>
+          <t>Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>2 registrados para Agosto 2026</t>
+          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
         </is>
       </c>
     </row>
@@ -6652,16 +6652,97 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Relatório de Gestão · Incentivado CDI 30</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Gerador de Relatório de Gestão · Incentivado CDI 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr">
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>cards de relatório</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2 registrados para Agosto 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
         <is>
           <t>data automática</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr">
         <is>
           <t>DATA_BASE=2026-08-31</t>
         </is>
@@ -13612,7 +13693,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>725951</v>
+        <v>726075</v>
       </c>
     </row>
     <row r="3">
@@ -13627,7 +13708,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47617</v>
+        <v>47631</v>
       </c>
     </row>
     <row r="4">
@@ -13642,7 +13723,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>735471</v>
+        <v>735702</v>
       </c>
     </row>
     <row r="5">
@@ -13657,7 +13738,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47825</v>
+        <v>47823</v>
       </c>
     </row>
     <row r="6">
@@ -13672,7 +13753,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>738135</v>
+        <v>738232</v>
       </c>
     </row>
     <row r="7">
@@ -13702,7 +13783,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>735713</v>
+        <v>735788</v>
       </c>
     </row>
     <row r="9">
@@ -13717,7 +13798,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47695</v>
+        <v>47693</v>
       </c>
     </row>
     <row r="10">
@@ -13732,7 +13813,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>722844</v>
+        <v>722777</v>
       </c>
     </row>
     <row r="11">
@@ -13747,7 +13828,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46726</v>
+        <v>46724</v>
       </c>
     </row>
     <row r="12">
@@ -13762,7 +13843,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>725040</v>
+        <v>725091</v>
       </c>
     </row>
     <row r="13">
@@ -13777,7 +13858,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47654</v>
+        <v>47652</v>
       </c>
     </row>
     <row r="14">
@@ -13792,7 +13873,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>725557</v>
+        <v>725922</v>
       </c>
     </row>
     <row r="15">
@@ -13807,7 +13888,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47690</v>
+        <v>47696</v>
       </c>
     </row>
     <row r="16">
@@ -13822,7 +13903,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>600312</v>
+        <v>654116</v>
       </c>
     </row>
     <row r="17">
@@ -13837,7 +13918,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>43231</v>
+        <v>43427</v>
       </c>
     </row>
     <row r="18">
@@ -13852,7 +13933,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>599523</v>
+        <v>646161</v>
       </c>
     </row>
     <row r="19">
@@ -13867,7 +13948,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43203</v>
+        <v>43362</v>
       </c>
     </row>
     <row r="20">
@@ -13882,7 +13963,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>615094</v>
+        <v>658504</v>
       </c>
     </row>
     <row r="21">
@@ -13897,7 +13978,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42086</v>
+        <v>42240</v>
       </c>
     </row>
     <row r="22">
@@ -13912,7 +13993,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>728860</v>
+        <v>728823</v>
       </c>
     </row>
     <row r="23">
@@ -13927,7 +14008,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47118</v>
+        <v>47115</v>
       </c>
     </row>
     <row r="24">
@@ -13942,7 +14023,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>722113</v>
+        <v>722104</v>
       </c>
     </row>
     <row r="25">
@@ -13957,7 +14038,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46714</v>
+        <v>46719</v>
       </c>
     </row>
     <row r="26">
@@ -13972,7 +14053,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>725368</v>
+        <v>726072</v>
       </c>
     </row>
     <row r="27">
@@ -13987,7 +14068,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47669</v>
+        <v>47683</v>
       </c>
     </row>
     <row r="28">
@@ -14002,7 +14083,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3080192</v>
+        <v>3084971</v>
       </c>
     </row>
     <row r="29">
@@ -14017,7 +14098,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>934672</v>
+        <v>1018985</v>
       </c>
     </row>
     <row r="30">
@@ -14047,7 +14128,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>130889</v>
+        <v>130928</v>
       </c>
     </row>
     <row r="32">
@@ -14092,7 +14173,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>126107</v>
+        <v>126116</v>
       </c>
     </row>
     <row r="35">
@@ -14122,7 +14203,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>121698</v>
+        <v>121950</v>
       </c>
     </row>
     <row r="37">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -13738,7 +13738,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47823</v>
+        <v>47824</v>
       </c>
     </row>
     <row r="6">
@@ -13768,7 +13768,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47843</v>
+        <v>47846</v>
       </c>
     </row>
     <row r="8">
@@ -13798,7 +13798,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47693</v>
+        <v>47696</v>
       </c>
     </row>
     <row r="10">
@@ -13828,7 +13828,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46724</v>
+        <v>46723</v>
       </c>
     </row>
     <row r="12">
@@ -13858,7 +13858,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47652</v>
+        <v>47653</v>
       </c>
     </row>
     <row r="14">
@@ -13888,7 +13888,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47696</v>
+        <v>47692</v>
       </c>
     </row>
     <row r="16">
@@ -13918,7 +13918,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>43427</v>
+        <v>43430</v>
       </c>
     </row>
     <row r="18">
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42240</v>
+        <v>42241</v>
       </c>
     </row>
     <row r="22">
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47115</v>
+        <v>47120</v>
       </c>
     </row>
     <row r="24">
@@ -14038,7 +14038,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46719</v>
+        <v>46716</v>
       </c>
     </row>
     <row r="26">
@@ -14068,7 +14068,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47683</v>
+        <v>47687</v>
       </c>
     </row>
     <row r="28">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -835,7 +835,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+50'], ['Benchmark', 'CDI'], ['Taxa de Performance', 'Não há'], ['Taxa global', '0,65% a.a.'], ['PL (desde o início)', 'R$ 26,8 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+50'], ['Benchmark', 'CDI'], ['Taxa de Performance', '15% do retorno que exceder CDI+0,65%'], ['Taxa global', '1,15% a.a.'], ['PL (desde o início)', 'R$ 26,8 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>[['Público Alvo', 'Investidores qualificados, Multi Family e Family Offices'], ['Resgate', 'D+180'], ['Benchmark', 'CDI'], ['Taxa de Performance', '20% do que exceder o CDI'], ['Taxa global', '1,15% a.a.'], ['PL Médio (12M)', 'R$ 94,5 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+          <t>[['Público Alvo', 'Investidores qualificados, Multi Family e Family Offices'], ['Resgate', 'D+180'], ['Benchmark', 'CDI'], ['Taxa de Performance', '20% do que exceder do CDI'], ['Taxa global', '1,15% a.a.'], ['PL Médio (12M)', 'R$ 94,5 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+90'], ['Benchmark', 'CDI'], ['Taxa de Performance', '10% do que exceder o CDI'], ['Taxa global', '2,43% a.a.'], ['PL Médio (12M)', 'R$ 15,7 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
+          <t>[['Público Alvo', 'Investidor qualificado'], ['Resgate', 'D+90'], ['Benchmark', 'CDI'], ['Taxa de Performance', '10% do que exceder do CDI'], ['Taxa global', '1,25% a.a.'], ['PL Médio (12M)', 'R$ 15,7 mi'], ['Aplicação Mínima', 'R$ 1.000,00']]</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Taxa global: 2,43% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
+          <t>Taxa global: 1,25% a.a. Taxa de performance: 10% do que exceder do CDI. Resgate: D+90.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Taxa global: 0,65% a.a. Taxa de performance: não há.</t>
+          <t>Taxa global: 1,15% a.a. Taxa de performance: 15% do retorno que exceder CDI+0,65%.</t>
         </is>
       </c>
     </row>
@@ -12550,7 +12550,7 @@
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -12831,7 +12831,11 @@
           <t>1,15% a.a.</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20% do que exceder do CDI</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>sim</t>
@@ -12856,10 +12860,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2,43% a.a.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>1,25% a.a.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10% do que exceder do CDI</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>sim</t>
@@ -12884,12 +12892,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0,65% a.a.</t>
+          <t>1,15% a.a.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Não há</t>
+          <t>15% do retorno que exceder CDI+0,65%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -13229,11 +13237,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="58" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -13359,287 +13367,66 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>relatorio/banks</t>
+          <t>relatorio/credito_privado</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>bvp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>relatorio/institucional</t>
+          <t>tivio-email-fundos-credito.html</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>relatorio/inst15</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>topgestormacro</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
+          <t>sem dados — rentabilidade e PL mantidos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>relatorio/inst30</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>relatorio/infraplus</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>relatorio/bvp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>relatorio/rfcp</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>relatorio/alt180</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>relatorio/alt90</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>relatorio/altlight</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>relatorio/infrapluscdi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>relatorio/esplanada</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>relatorio/legacy</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>fonte Versos não carregou (CDN inacessível?) — o PDF sai com a fonte de fallback e a métrica do texto muda</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>relatorio/credito_privado</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>bvp</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>tivio-email-fundos-credito.html</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>alt180</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>tivio-post-investment-solutions.html</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>topgestormacro</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>sem dados — rentabilidade e PL mantidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
         <is>
           <t>card "Gerador de Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
         </is>
@@ -13693,7 +13480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>726075</v>
+        <v>704633</v>
       </c>
     </row>
     <row r="3">
@@ -13708,7 +13495,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47631</v>
+        <v>47632</v>
       </c>
     </row>
     <row r="4">
@@ -13723,7 +13510,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>735702</v>
+        <v>710959</v>
       </c>
     </row>
     <row r="5">
@@ -13738,7 +13525,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47824</v>
+        <v>47827</v>
       </c>
     </row>
     <row r="6">
@@ -13753,7 +13540,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>738232</v>
+        <v>714908</v>
       </c>
     </row>
     <row r="7">
@@ -13768,7 +13555,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47846</v>
+        <v>47847</v>
       </c>
     </row>
     <row r="8">
@@ -13783,7 +13570,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>735788</v>
+        <v>713283</v>
       </c>
     </row>
     <row r="9">
@@ -13798,7 +13585,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47696</v>
+        <v>47693</v>
       </c>
     </row>
     <row r="10">
@@ -13813,7 +13600,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>722777</v>
+        <v>701041</v>
       </c>
     </row>
     <row r="11">
@@ -13828,7 +13615,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46723</v>
+        <v>46725</v>
       </c>
     </row>
     <row r="12">
@@ -13843,7 +13630,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>725091</v>
+        <v>695670</v>
       </c>
     </row>
     <row r="13">
@@ -13858,7 +13645,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47653</v>
+        <v>47654</v>
       </c>
     </row>
     <row r="14">
@@ -13873,7 +13660,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>725922</v>
+        <v>704831</v>
       </c>
     </row>
     <row r="15">
@@ -13888,7 +13675,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47692</v>
+        <v>47696</v>
       </c>
     </row>
     <row r="16">
@@ -13903,7 +13690,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>654116</v>
+        <v>625363</v>
       </c>
     </row>
     <row r="17">
@@ -13918,7 +13705,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>43430</v>
+        <v>43631</v>
       </c>
     </row>
     <row r="18">
@@ -13933,7 +13720,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>646161</v>
+        <v>624108</v>
       </c>
     </row>
     <row r="19">
@@ -13948,7 +13735,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43362</v>
+        <v>43543</v>
       </c>
     </row>
     <row r="20">
@@ -13963,7 +13750,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>658504</v>
+        <v>625103</v>
       </c>
     </row>
     <row r="21">
@@ -13978,7 +13765,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42241</v>
+        <v>42431</v>
       </c>
     </row>
     <row r="22">
@@ -13993,7 +13780,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>728823</v>
+        <v>704469</v>
       </c>
     </row>
     <row r="23">
@@ -14008,7 +13795,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47120</v>
+        <v>47123</v>
       </c>
     </row>
     <row r="24">
@@ -14023,7 +13810,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>722104</v>
+        <v>706708</v>
       </c>
     </row>
     <row r="25">
@@ -14038,7 +13825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46716</v>
+        <v>46715</v>
       </c>
     </row>
     <row r="26">
@@ -14053,7 +13840,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>726072</v>
+        <v>712840</v>
       </c>
     </row>
     <row r="27">
@@ -14068,7 +13855,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47687</v>
+        <v>47688</v>
       </c>
     </row>
     <row r="28">
@@ -14083,7 +13870,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3084971</v>
+        <v>3212506</v>
       </c>
     </row>
     <row r="29">
@@ -14098,7 +13885,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1018985</v>
+        <v>1055001</v>
       </c>
     </row>
     <row r="30">
@@ -14113,7 +13900,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>87214</v>
+        <v>88026</v>
       </c>
     </row>
     <row r="31">
@@ -14128,7 +13915,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>130928</v>
+        <v>131775</v>
       </c>
     </row>
     <row r="32">
@@ -14143,7 +13930,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49750</v>
+        <v>50202</v>
       </c>
     </row>
     <row r="33">
@@ -14158,7 +13945,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>113302</v>
+        <v>114702</v>
       </c>
     </row>
     <row r="34">
@@ -14173,7 +13960,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>126116</v>
+        <v>127504</v>
       </c>
     </row>
     <row r="35">
@@ -14188,7 +13975,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>103643</v>
+        <v>104943</v>
       </c>
     </row>
     <row r="36">
@@ -14203,7 +13990,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>121950</v>
+        <v>122525</v>
       </c>
     </row>
     <row r="37">
@@ -14218,7 +14005,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>66082</v>
+        <v>66613</v>
       </c>
     </row>
   </sheetData>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -13480,7 +13480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>704633</v>
+        <v>832184</v>
       </c>
     </row>
     <row r="3">
@@ -13495,7 +13495,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47632</v>
+        <v>47637</v>
       </c>
     </row>
     <row r="4">
@@ -13510,7 +13510,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>710959</v>
+        <v>838500</v>
       </c>
     </row>
     <row r="5">
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47827</v>
+        <v>47824</v>
       </c>
     </row>
     <row r="6">
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>714908</v>
+        <v>842446</v>
       </c>
     </row>
     <row r="7">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47847</v>
+        <v>47848</v>
       </c>
     </row>
     <row r="8">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>713283</v>
+        <v>840983</v>
       </c>
     </row>
     <row r="9">
@@ -13585,7 +13585,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47693</v>
+        <v>47696</v>
       </c>
     </row>
     <row r="10">
@@ -13600,7 +13600,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>701041</v>
+        <v>791785</v>
       </c>
     </row>
     <row r="11">
@@ -13615,7 +13615,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46725</v>
+        <v>46722</v>
       </c>
     </row>
     <row r="12">
@@ -13630,7 +13630,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>695670</v>
+        <v>823202</v>
       </c>
     </row>
     <row r="13">
@@ -13645,7 +13645,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47654</v>
+        <v>47651</v>
       </c>
     </row>
     <row r="14">
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>704831</v>
+        <v>832443</v>
       </c>
     </row>
     <row r="15">
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47696</v>
+        <v>47697</v>
       </c>
     </row>
     <row r="16">
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43543</v>
+        <v>43545</v>
       </c>
     </row>
     <row r="20">
@@ -13765,7 +13765,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42431</v>
+        <v>42429</v>
       </c>
     </row>
     <row r="22">
@@ -13780,7 +13780,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>704469</v>
+        <v>832111</v>
       </c>
     </row>
     <row r="23">
@@ -13795,7 +13795,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47123</v>
+        <v>47118</v>
       </c>
     </row>
     <row r="24">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>706708</v>
+        <v>797583</v>
       </c>
     </row>
     <row r="25">
@@ -13825,7 +13825,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46715</v>
+        <v>46717</v>
       </c>
     </row>
     <row r="26">
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>712840</v>
+        <v>840434</v>
       </c>
     </row>
     <row r="27">
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47688</v>
+        <v>47685</v>
       </c>
     </row>
     <row r="28">
@@ -13870,7 +13870,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3212506</v>
+        <v>3218147</v>
       </c>
     </row>
     <row r="29">
@@ -13885,7 +13885,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1055001</v>
+        <v>1060312</v>
       </c>
     </row>
     <row r="30">
@@ -13915,7 +13915,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>131775</v>
+        <v>176798</v>
       </c>
     </row>
     <row r="32">
@@ -13975,7 +13975,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>104943</v>
+        <v>105529</v>
       </c>
     </row>
     <row r="36">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -424,10 +424,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E234"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
@@ -4568,2181 +4568,210 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>mercado</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>MARKET</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>[['Total', '446.217', '100,0%', '1,14%', '1,17%', '-0,03%', '2,86', True], ['Energia elétrica', '102.982', '23,11%', '0,75%', '0,76%', '-0,02%', '2,78', False], ['Assistência médica', '45.853', '10,29%', '1,45%', '1,48%', '-0,04%', '3,40', False], ['Locação de veículos', '43.937', '9,86%', '1,72%', '1,71%', '0,02%', '2,51', False], ['Saneamento', '40.735', '9,14%', '1,43%', '1,44%', '-0,01%', '2,87', False], ['Petróleo e gás', '33.732', '7,57%', '0,91%', '0,95%', '-0,04%', '3,01', False], ['Transporte e logística', '27.250', '6,11%', '1,41%', '1,54%', '-0,12%', '2,78', False], ['Comércio atacadista e varejista', '24.639', '5,53%', '1,33%', '1,39%', '-0,06%', '2,65', False], ['Financeiro', '23.379', '5,25%', '0,52%', '0,54%', '-0,02%', '2,38', False], ['Indústria e comércio', '20.251', '4,54%', '1,15%', '1,20%', '-0,04%', '2,82', False], ['TI e telecomunicações', '17.577', '3,94%', '1,11%', '1,12%', '-0,01%', '2,46', False], ['Bioenergia', '11.334', '2,54%', '1,74%', '1,80%', '-0,06%', '3,08', False], ['Metalurgia e siderurgia', '9.560', '2,15%', '1,25%', '1,15%', '0,10%', '3,10', False], ['Educação', '7.933', '1,78%', '1,02%', '1,06%', '-0,04%', '2,39', False], ['Outros serviços', '7.003', '1,57%', '1,10%', '1,12%', '-0,02%', '2,89', False], ['Empreendimentos e participações', '6.693', '1,50%', '1,23%', '1,24%', '-0,01%', '3,44', False], ['Serviços imobiliários', '6.353', '1,43%', '0,64%', '0,65%', '-0,01%', '3,62', False], ['Papel e Celulose', '5.247', '1,18%', '0,58%', '0,60%', '-0,03%', '4,73', False], ['Materiais de construção e agregados', '4.144', '0,93%', '1,04%', '1,04%', '0,00%', '3,64', False], ['Química e petroquímica', '2.554', '0,57%', '1,11%', '1,14%', '-0,03%', '3,75', False], ['Alimentos e bebidas', '1.727', '0,39%', '1,25%', '1,28%', '-0,03%', '1,37', False], ['Têxtil e calçados', '1.528', '0,34%', '1,25%', '1,25%', '0,00%', '2,90', False], ['Mineração', '1.072', '0,24%', '0,83%', '0,86%', '-0,03%', '2,51', False], ['Construção civil', '166', '0,04%', '1,66%', '1,82%', '-0,16%', '0,68', False]]</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>[['Setor', 'Volume (R$ MM)', '%', 'Spread Atual', 'Spread mês anterior', 'Variação', 'Duration', False], ['Total', '(a linha Total vem primeiro)', '', '', '', '', '', True]]</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>pl</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>R$ 1.698.520.740,05</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>R$ 1.793.381.077,96</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>s8</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>plm</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>R$ 1.397.203.402,03</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>R$ 1.449.683.179,97</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>e1</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>perfrows</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'pct': ['101%', '100%', '100%']}</t>
+          <t>Julho 2026</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>{'fundo': ['1,10%', '9,36%', '14,63%', '29,82%', '45,41%', '444,67%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '408,92%'], 'pct': ['100,59%', '100,31%', '100,43%', '101,12%', '102,80%', '108,74%'], 'alfa': ['0,01%', '0,03%', '0,06%', '0,33%', '1,24%', '35,75%']}</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>r2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>emissores</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>[['ITAÚ UNIBANCO', '3,42%', 100], ['BRADESCO', '3,18%', 93], ['SANTANDER', '2,86%', 84], ['BANCO DO BRASIL', '2,54%', 74], ['BTG PACTUAL', '2,21%', 65]]</t>
+          <t>Relatório de Gestão · Incentivado CDI 30</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>[['BV', '6,36%', 100], ['XP', '6,04%', 95], ['BTG', '5,97%', 94], ['ABC', '5,92%', 93], ['NUBANK', '5,57%', 88]]</t>
+          <t>Gerador de Relatório de Gestão · Incentivado CDI 30</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>r2</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>setores</t>
+          <t>desc</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[['Financeiro', '76,5%'], ['Caixa', '23,5%']]</t>
+          <t>Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>[['Financeiro', '75,7%'], ['Caixa', '24,2%']]</t>
+          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
+          <t>cards de relatório</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>[['AAA', '50,8%', 100], ['AA+', '16,3%', 32], ['AA', '2,0%', 4], ['A+', '1,9%', 4], ['A', '3,0%', 6]]</t>
+          <t>2 registrados para Agosto 2026</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
+          <t>data automática</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>banks</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1,12</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>banks</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>hist12</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.23, 2.53, 3.62, 4.88, 6.11, 7.18, 8.48, 9.64, 10.82, 12.07, 13.45, 14.7], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>banks</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>histEnd</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>[12.0, 12.0, 'CDI']</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>[14.7, 14.63, 'CDI']</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>banks</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O BANKS apresentou rentabilidade de &lt;b&gt;1,01%&lt;/b&gt; no mês (&lt;b&gt;101% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,17%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>['O Fundo Tivio Banks obteve retorno de 1,10% (101% do CDI) no mês e acumula 9,36% (100% do CDI) em 2026. A alocação em crédito era de 75%, integralmente concentrada em emissores do setor bancário. O carrego da carteira encontra-se em CDI +0,25%, com duration média de 1,05 ano.', 'Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>R$ 1.983.487.947,49</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>R$ 1.815.644.128,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>plm</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>R$ 2.522.009.705,73</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>R$ 2.491.331.200,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>perfrows</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>{'pct': ['104%', '100%', '100%']}</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>{'fundo': ['1,09%', '9,31%', '14,58%', '29,93%', '47,60%', '825,45%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '753,88%'], 'pct': ['100%', '100%', '100%', '102%', '108%', '109%'], 'alfa': ['−0,01%', '−0,02%', '0,01%', '0,44%', '3,43%', '71,57%']}</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>emissores</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>[['AEGEA', '2,64%', 100], ['TUPY', '2,31%', 88], ['VALE', '2,05%', 78], ['PETROBRAS', '1,86%', 70], ['RANDON', '1,52%', 58]]</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>[['BTG', '3,45%', 100], ['BB', '3,44%', 100], ['SANTANDER', '3,06%', 89], ['SAFRA', '3,02%', 88], ['BRADESCO', '2,89%', 84]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>setores</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '52%'], ['Energia Elétrica', '4%'], ['Transporte e Logística', '2%'], ['Saneamento', '2%'], ['Caixa', '31%']]</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '44,6%'], ['Energia Elétrica', '4,5%'], ['FIDC', '2,1%'], ['Transporte e Logística', '2,1%'], ['Saneamento', '2,0%'], ['Caixa', '38,7%']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>[['AAA', '39,6%', 100], ['AA+', '10,5%', 27], ['AA', '2,4%', 6], ['AA-', '2,7%', 7], ['A+', '1,2%', 3], ['A', '3,3%', 8]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>1,20</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>hist12</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.25, 2.52, 3.59, 4.88, 6.12, 7.13, 8.29, 9.43, 10.74, 11.99, 13.41, 14.64], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>histEnd</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>[12.48, 12.0, 'CDI']</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>[14.64, 14.63, 'CDI']</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>institucional</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL apresentou rentabilidade de &lt;b&gt;1,27%&lt;/b&gt; no mês (&lt;b&gt;104% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,13%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Fundo Tivio Institucional apresentou rentabilidade de 1,09% no mês (100% do CDI), acumulando 9,31% (100% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Argo e Aegea, enquanto Aegea foi o maior detrator.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>adm</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>0,45% a.a.</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>0,50% a.a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>Não há</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>20% do que exceder 102,5% do CDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>R$ 161.593.743,98</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>R$ 156.046.891,63</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>plm</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>R$ 140.997.685,81</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>R$ 146.843.921,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>perfrows</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>{'pct': ['113%', '102%', '102%']}</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>{'fundo': ['1,11%', '9,53%', '14,94%', '30,92%', '51,22%', '1.644,37%'], 'bench': ['1,09%', '9,33%', '14,57%', '29,49%', '44,17%', '1.408,13%'], 'pct': ['102%', '102%', '103%', '105%', '116%', '117%'], 'alfa': ['0,02%', '0,20%', '0,36%', '1,43%', '7,05%', '236,24%']}</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>emissores</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>[['TUPY', '3,04%', 100], ['UNIDAS', '2,71%', 89], ['AEGEA', '2,33%', 77], ['HAPVIDA', '2,01%', 66], ['EQUATORIAL', '1,74%', 57]]</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>[['C6', '5,45%', 100], ['ABC', '3,43%', 63], ['XP', '3,28%', 60], ['BTG', '3,28%', 60], ['BRADESCO', '1,76%', 32]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>setores</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '29%'], ['FIDC', '13%'], ['Energia Elétrica', '7%'], ['Saneamento', '5%'], ['Transporte e Logística', '4%'], ['Caixa', '26%']]</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '28,0%'], ['FIDC', '13,0%'], ['Energia Elétrica', '7,1%'], ['Locação de veículos', '3,8%'], ['Saneamento', '3,5%'], ['Caixa', '27,2%']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>[['AAA', '32,7%', 100], ['AA+', '7,8%', 24], ['AA', '4,1%', 13], ['AA-', '5,7%', 17], ['A+', '4,2%', 13], ['A', '6,2%', 19]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>1,00%</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>1,80</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>anos</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>hist12</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.29, 2.5, 3.53, 5.0, 6.31, 7.33, 8.3, 9.48, 10.88, 12.2, 13.74, 15.0], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>histEnd</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>[12.24, 12.0, 'CDI']</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>[15.0, 14.63, 'CDI']</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 15 apresentou rentabilidade de &lt;b&gt;1,37%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,32%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 15 apresentou rentabilidade de 1,11% no mês (102% do CDI), acumulando 9,53% (102% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>adm</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>0,63% a.a.</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>0,625% a.a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>20% do que exceder o CDI</t>
-        </is>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>20% do que exceder 100% do CDI</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>R$ 143.232.764,20</t>
-        </is>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>R$ 126.168.780,56</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>plm</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>R$ 155.004.649,74</t>
-        </is>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>R$ 158.893.390,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>perfrows</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>{'pct': ['113%', '101%', '101%']}</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>{'fundo': ['1,12%', '9,45%', '14,68%', '−', '−', '25,93%'], 'bench': ['1,09%', '9,33%', '14,57%', '−', '−', '25,71%'], 'pct': ['102%', '101%', '101%', '−', '−', '101%'], 'alfa': ['0,03%', '0,12%', '0,11%', '−', '−', '0,21%']}</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>emissores</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>[['AEGEA', '2,88%', 100], ['EQUATORIAL', '2,55%', 89], ['TUPY', '2,22%', 77], ['SABESP', '1,94%', 67], ['ENGIE', '1,67%', 58]]</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>[['C6', '6,00%', 100], ['ABC', '3,78%', 63], ['XP', '3,62%', 60], ['BTG', '3,62%', 60], ['BRADESCO', '1,94%', 32]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>setores</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '33%'], ['FIDC', '15%'], ['Energia Elétrica', '8%'], ['Saneamento', '6%'], ['Transporte e Logística', '5%'], ['Caixa', '16%']]</t>
-        </is>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>[['Financeiro', '30,8%'], ['FIDC', '14,4%'], ['Energia Elétrica', '7,8%'], ['Locação de veículos', '4,2%'], ['Saneamento', '3,8%'], ['Caixa', '19,7%']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>[['AAA', '46,2%', 100], ['AA+', '24,8%', 54], ['AA', '14,1%', 31], ['AA-', '9,4%', 20], ['A+', '3,9%', 8], ['A', '1,6%', 3]]</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>[['AAA', '36,0%', 100], ['AA+', '8,6%', 24], ['AA', '4,5%', 13], ['AA-', '6,2%', 17], ['A+', '4,7%', 13], ['A', '6,8%', 19]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>1,86</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>anos</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>hist12</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>{'b': 'CDI', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.3, 2.52, 3.56, 4.85, 6.13, 7.14, 8.01, 9.16, 10.62, 11.95, 13.48, 14.75], 'c': [0.0, 1.22, 2.51, 3.59, 4.85, 6.07, 7.13, 8.43, 9.61, 10.79, 12.03, 13.39, 14.63]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>histEnd</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>[12.12, 12.0, 'CDI']</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>[14.75, 14.63, 'CDI']</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>['No mês, o mercado de crédito privado high grade manteve o movimento de fechamento gradual de spreads, com fluxo comprador consistente no secundário e oferta primária ainda concentrada em emissores de primeira linha.', 'A liquidez permaneceu saudável ao longo da curva, com boa demanda por papéis bancários e por debêntures de empresas de energia, saneamento e infraestrutura, setores de maior peso na carteira.', 'Do ponto de vista da gestão, seguimos priorizando emissores de baixo risco de crédito e o controle da duration, mantendo carrego atrativo sobre o CDI sem elevar de forma relevante a volatilidade da cota.', 'O INSTITUCIONAL 30 apresentou rentabilidade de &lt;b&gt;1,36%&lt;/b&gt; no mês (&lt;b&gt;113% do CDI&lt;/b&gt;), acumulando &lt;b&gt;8,08%&lt;/b&gt; no ano. Os principais atribuidores de resultado foram as debêntures corporativas e a parcela bancária da carteira.']</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>['Em agosto, o mercado de crédito foi marcado por um ambiente de menor liquidez nas negociações do mercado secundário e por uma leve reabertura dos spreads de crédito. Após meses consecutivos de compressão dos prêmios de risco, observou-se um movimento mais cauteloso por parte dos investidores, com os spreads médios dos títulos corporativos indexados ao CDI avançando aproximadamente 0,03%, passando de CDI + 1,19% para CDI + 1,22% ao ano. Apesar desse ajuste, os níveis de prêmio permaneceram próximos das mínimas históricas observadas ao longo do ciclo recente.', 'No mercado secundário, a redução do volume negociado contribuiu para uma formação de preços mais seletiva, especialmente em ativos corporativos com menor liquidez. Ainda assim, o comportamento dos investidores permaneceu construtivo, sustentado por um ambiente técnico favorável e pela continuidade da elevada demanda por ativos de crédito.', 'Já no mercado primário, as emissões bancárias seguiram registrando forte demanda por parte dos investidores. As ofertas de Letras Financeiras Seniores distribuídas ao longo do mês apresentaram níveis elevados de subscrição, com demanda que, em diversos casos, superou três vezes o volume ofertado. Esse forte apetite permitiu que as operações fossem precificadas com taxas inferiores aos limites inicialmente indicados pelos emissores, evidenciando a elevada disponibilidade de recursos para alocação na indústria de crédito. Por outro lado, o pipeline de emissões corporativas permaneceu limitado, restringindo a oferta de novos ativos em um momento de demanda ainda aquecida.', 'Em relação aos fluxos, os fundos com alocação mínima de 15% em crédito e ao menos 1% em debêntures apresentaram captação líquida próxima de R$ 8 bilhões em agosto, resultado significativamente superior ao observado no mês anterior. O volume reforça a percepção de que os investidores seguem direcionando recursos para estratégias de crédito, impulsionados pelo elevado nível de carrego proporcionado pelos ativos indexados ao CDI e pela busca por alternativas de investimento com perfil de risco-retorno atrativo.', 'Nesse contexto, a combinação entre fluxos positivos para a indústria, vencimentos e amortizações recorrentes das carteiras, além da limitada oferta de novos ativos corporativos, continuou sustentando a demanda por crédito privado. Ainda que agosto tenha apresentado uma leve reabertura dos spreads médios de mercado, a dinâmica técnica permanece favorável e os prêmios seguem negociando em patamares historicamente reduzidos.', 'Por fim, sob a ótica da gestão, seguimos acompanhando de forma criteriosa a evolução dos fundamentos dos emissores presentes nas carteiras, com atenção especial aos indicadores operacionais, à geração de caixa e à manutenção de estruturas de capital adequadas. Em um ambiente em que os spreads permanecem comprimidos em termos históricos, mantemos disciplina na alocação dos recursos, priorizando operações que apresentem adequada relação entre risco e retorno e preservando flexibilidade para captura de oportunidades que possam surgir em eventuais períodos de maior volatilidade do mercado.', 'Nesse cenário, o Tivio Institucional 30 apresentou rentabilidade de 1,12% no mês (102% do CDI), acumulando 9,45% (101% do CDI) no ano. Na parcela de corporativos, os maiores atribuidores de resultado foram para Tupy e Randon, enquanto Hapvida foi o maior detrator.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>pl</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>R$ 42.983.282,75</t>
-        </is>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>R$ 42.694.019,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>plm</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>R$ 52.049.593,91</t>
-        </is>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>R$ 49.421.174,50</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>perfrows</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>{'abs': ['1,24%', '7,80%', '12,94%'], 'alfa': ['−0,14%', '−3,14%', '−2,75%']}</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>{'fundo': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'bench': ['1,28%', '9,18%', '13,34%', '23,32%', '33,11%', '87,91%'], 'abs': ['1,26%', '5,98%', '9,91%', '19,03%', '29,49%', '77,41%'], 'alfa': ['−0,01%', '−3,20%', '−3,44%', '−4,28%', '−3,62%', '−10,50%']}</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>emissores</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>[['EQUATORIAL', '3,87%', 100], ['CEMIG', '3,42%', 88], ['COPEL', '3,14%', 81], ['SABESP', '3,03%', 78], ['ELETROBRAS', '2,92%', 75]]</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>[['AUREN', '7,68%', 100], ['EQUATORIAL', '7,24%', 94], ['EDF', '5,54%', 72], ['SINOP', '3,99%', 52], ['ELETROBRAS', '3,65%', 48]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>setores</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>[['Energia Elétrica', '55%'], ['Transporte e Logística', '15%'], ['Saneamento', '7%'], ['Petróleo e Gás', '5%'], ['TI e Telecomunicações', '4%'], ['Caixa', '5%']]</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>[['Energia Elétrica', '55,9%'], ['Transporte e Logística', '15,3%'], ['Saneamento', '7,3%'], ['TI e Telecomunicações', '5,4%'], ['Petróleo e Gás', '4,8%'], ['Caixa', '4,8%']]</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>[['AAA', '32,35%', 100], ['AA+', '17,91%', 55], ['AA', '11,27%', 35], ['AA-', '15,61%', 48], ['A+', '7,15%', 22], ['A', '1,85%', 6]]</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>[['AAA', '35,4%', 100], ['AA+', '26,0%', 74], ['AA', '11,1%', 31], ['AA-', '8,8%', 25], ['A+', '5,1%', 14], ['A', '2,4%', 7]]</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>val</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>3,98</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>hist12</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>{'b': 'IMA-B 5', 'l': ['2025-08', '2025-09', '2025-10', '2025-11', '2025-12', '2026-01', '2026-02', '2026-03', '2026-04', '2026-05', '2026-06', '2026-07', '2026-08'], 'f': [0.0, 1.64, 1.66, 3.1, 3.59, 5.89, 6.95, 6.67, 6.97, 7.26, 7.24, 8.41, 9.78], 'c': [0.0, 0.66, 1.69, 2.78, 3.76, 5.01, 6.29, 7.77, 9.19, 10.24, 10.48, 11.85, 13.28]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>histEnd</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>[12.94, 15.69, 'IMA-B 5']</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>[9.78, 13.28, 'IMA-B 5']</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>comentario</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>['Em julho, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho negativo, refletindo a elevação da curva real de juros ao longo do período. Embora os spreads de crédito tenham fechado cerca de 16 bps em relação ao mês anterior, o avanço da curva de juros reais prevaleceu sobre esse efeito.', 'No mercado primário, manteve-se o cenário de oferta restrita, com parcela relevante das emissões sendo absorvida pelos balanços dos bancos distribuidores. No secundário, houve retomada da demanda por papéis incentivados, inclusive nos vencimentos mais longos.', 'Do ponto de vista da gestão, mantivemos postura cautelosa, priorizando o encurtamento da duration da carteira como forma de mitigar volatilidade e reduzir a sensibilidade a movimentos adversos nos spreads.', 'O Infra Plus apresentou rentabilidade, isenta de imposto de renda, de &lt;b&gt;1,24%&lt;/b&gt; no mês, acumulando &lt;b&gt;7,80%&lt;/b&gt; no ano. Destacam-se as debêntures de RUMO e NTS, enquanto Alloha Fibra foi a maior detratora.']</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>['Em agosto, os títulos de crédito indexados ao IPCA precificados pela ANBIMA apresentaram desempenho positivo, refletindo principalmente o movimento de fechamento da curva real de juros observado ao longo do período. Embora os spreads de crédito tenham registrado abertura média de aproximadamente 5 bps em relação a julho, a redução das taxas reais ao longo da estrutura a termo mais do que compensou esse movimento. Como resultado, as taxas médias dos títulos incentivados precificados pela ANBIMA encerraram o mês com fechamento próximo de 16 bps, proporcionando valorização dos ativos no mercado secundário.', 'No mercado primário, manteve-se o cenário de oferta restrita de ativos, com parcela relevante das emissões sendo absorvida diretamente pelos balanços dos bancos distribuidores. Já no mercado secundário, observou-se um nível de liquidez inferior à média observada ao longo de 2025, contribuindo para um ambiente de maior equilíbrio entre oferta e demanda dos ativos negociados.', 'Sob a ótica da gestão, mantivemos uma postura cautelosa ao longo do período, priorizando o encurtamento da duration da carteira como forma de mitigar a volatilidade e reduzir a sensibilidade do portfólio a eventuais movimentos adversos nos spreads de crédito. Apesar da melhora observada no desempenho dos ativos incentivados no mês, seguimos avaliando que os níveis atuais de prêmio ainda oferecem pouca margem de segurança frente aos riscos inerentes à classe. Dessa forma, permanecemos atentos à evolução das condições de mercado e à dinâmica de precificação dos ativos, buscando identificar oportunidades mais atrativas para aumentar a exposição ao risco de crédito de forma gradual e criteriosa, quando a relação risco-retorno se mostrar mais favorável.', 'Nesse cenário, o Tivio Infra Plus apresentou rentabilidade, isenta de imposto de renda de 1,26% no mês, acumulando 5,98% no ano. Na atribuição de performance, pode-se destacar as debêntures de NTS e São Simão, enquanto as de Jalles Machado foram as maiores detratoras.']</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>31/07/2026</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>Julho de 2026</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>Agosto de 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>julho de 2026</t>
-        </is>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>agosto de 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>-jul26</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-ago26</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>julho/2026</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>agosto/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>const A=6;const track</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>const A=7;const track</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>libs de exportação</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>CDN</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>4 referências → vendor/ local (CDN como reserva)</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>s1</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>s2</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>s8</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>r1</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>e1</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>Julho 2026</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>r1</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>Relatórios de Gestão · Crédito Privado</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>Gerador de Relatório de Gestão · Crédito Privado</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>r1</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório completo de 4 páginas (A4) por fundo, Banks, Institucional, Institucional 15, Institucional 30 e Infra Plus: objetivo, rentabilidade, emissores, alocação e rating; histórico e comentário do gestor; mercado de crédito; e características + disclaimer. Exportação em JPG e PDF.</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>r2</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>Relatório de Gestão · Incentivado CDI 30</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>Gerador de Relatório de Gestão · Incentivado CDI 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>r2</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>Construtor interativo, folha a folha. Os relatórios prontos do mês estão no card acima. Relatório de gestão mensal do Tivio Institucional Inc CDI 30 FIF (debêntures incentivadas · CDI).</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Central</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>cards de relatório</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>2 registrados para Agosto 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>data automática</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
-      <c r="E234" t="inlineStr">
         <is>
           <t>DATA_BASE=2026-08-31</t>
         </is>
@@ -13443,7 +11472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -13480,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>832184</v>
+        <v>833662</v>
       </c>
     </row>
     <row r="3">
@@ -13495,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>47637</v>
+        <v>1923065</v>
       </c>
     </row>
     <row r="4">
@@ -13510,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>838500</v>
+        <v>839985</v>
       </c>
     </row>
     <row r="5">
@@ -13525,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47824</v>
+        <v>1927590</v>
       </c>
     </row>
     <row r="6">
@@ -13540,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>842446</v>
+        <v>843920</v>
       </c>
     </row>
     <row r="7">
@@ -13555,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>47848</v>
+        <v>1946164</v>
       </c>
     </row>
     <row r="8">
@@ -13570,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>840983</v>
+        <v>842461</v>
       </c>
     </row>
     <row r="9">
@@ -13585,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47696</v>
+        <v>1919224</v>
       </c>
     </row>
     <row r="10">
@@ -13600,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>791785</v>
+        <v>793274</v>
       </c>
     </row>
     <row r="11">
@@ -13615,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46722</v>
+        <v>1560554</v>
       </c>
     </row>
     <row r="12">
@@ -13630,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>823202</v>
+        <v>824673</v>
       </c>
     </row>
     <row r="13">
@@ -13645,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>47651</v>
+        <v>1897910</v>
       </c>
     </row>
     <row r="14">
@@ -13660,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>832443</v>
+        <v>833914</v>
       </c>
     </row>
     <row r="15">
@@ -13675,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>47697</v>
+        <v>1916306</v>
       </c>
     </row>
     <row r="16">
@@ -13690,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>625363</v>
+        <v>626351</v>
       </c>
     </row>
     <row r="17">
@@ -13705,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>43631</v>
+        <v>305920</v>
       </c>
     </row>
     <row r="18">
@@ -13720,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>624108</v>
+        <v>625115</v>
       </c>
     </row>
     <row r="19">
@@ -13735,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43545</v>
+        <v>287034</v>
       </c>
     </row>
     <row r="20">
@@ -13750,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>625103</v>
+        <v>626121</v>
       </c>
     </row>
     <row r="21">
@@ -13765,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>42429</v>
+        <v>283919</v>
       </c>
     </row>
     <row r="22">
@@ -13780,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>832111</v>
+        <v>833629</v>
       </c>
     </row>
     <row r="23">
@@ -13795,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>47118</v>
+        <v>1909635</v>
       </c>
     </row>
     <row r="24">
@@ -13810,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>797583</v>
+        <v>793857</v>
       </c>
     </row>
     <row r="25">
@@ -13825,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>46717</v>
+        <v>1560004</v>
       </c>
     </row>
     <row r="26">
@@ -13840,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>840434</v>
+        <v>835600</v>
       </c>
     </row>
     <row r="27">
@@ -13855,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>47685</v>
+        <v>1919014</v>
       </c>
     </row>
     <row r="28">
@@ -13870,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3218147</v>
+        <v>3239620</v>
       </c>
     </row>
     <row r="29">
@@ -13885,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1060312</v>
+        <v>1060313</v>
       </c>
     </row>
     <row r="30">
@@ -13981,7 +12010,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tivio-relatorio-gestao-credito-privado.html</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -13990,22 +12019,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>122525</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>66613</v>
+        <v>65870</v>
       </c>
     </row>
   </sheetData>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>843920</v>
+        <v>843923</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1946164</v>
+        <v>1945550</v>
       </c>
     </row>
     <row r="8">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>626351</v>
+        <v>626383</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>305920</v>
+        <v>302078</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>625115</v>
+        <v>625093</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>287034</v>
+        <v>287505</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>626121</v>
+        <v>626284</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>283919</v>
+        <v>283711</v>
       </c>
     </row>
     <row r="22">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3239620</v>
+        <v>3239874</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1060313</v>
+        <v>1060177</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>833662</v>
+        <v>833143</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1923065</v>
+        <v>1906738</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>839985</v>
+        <v>839467</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1927590</v>
+        <v>1911437</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>843923</v>
+        <v>843406</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1945550</v>
+        <v>1928988</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>842461</v>
+        <v>841944</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1919224</v>
+        <v>1903123</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>793274</v>
+        <v>812058</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1560554</v>
+        <v>1901979</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>824673</v>
+        <v>824156</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1897910</v>
+        <v>1881925</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>833914</v>
+        <v>833399</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1916306</v>
+        <v>1900669</v>
       </c>
     </row>
     <row r="16">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>833629</v>
+        <v>833112</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1909635</v>
+        <v>1893613</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>793857</v>
+        <v>812654</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1560004</v>
+        <v>1900777</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>835600</v>
+        <v>835083</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1919014</v>
+        <v>1903091</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3239874</v>
+        <v>3240157</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1060177</v>
+        <v>1060460</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11472,7 +11472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>833143</v>
+        <v>837374</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1906738</v>
+        <v>1954048</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>839467</v>
+        <v>844142</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1911437</v>
+        <v>1967345</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>843406</v>
+        <v>848407</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1928988</v>
+        <v>1982981</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>841944</v>
+        <v>844766</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1903123</v>
+        <v>1962152</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>812058</v>
+        <v>815775</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1901979</v>
+        <v>1947337</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>824156</v>
+        <v>826969</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1881925</v>
+        <v>1928179</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>833399</v>
+        <v>836891</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1900669</v>
+        <v>1954540</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>626383</v>
+        <v>624863</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>302078</v>
+        <v>300733</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>625093</v>
+        <v>623155</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>287505</v>
+        <v>286918</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>626284</v>
+        <v>624241</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>283711</v>
+        <v>276744</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>833112</v>
+        <v>835949</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1893613</v>
+        <v>1951625</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>812654</v>
+        <v>815817</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1900777</v>
+        <v>1948754</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>835083</v>
+        <v>838848</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1903091</v>
+        <v>1954799</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3240157</v>
+        <v>3254516</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1060460</v>
+        <v>1063789</v>
       </c>
     </row>
     <row r="30">
@@ -11959,7 +11959,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50202</v>
+        <v>50469</v>
       </c>
     </row>
     <row r="33">
@@ -12020,6 +12020,21 @@
       </c>
       <c r="C36" t="n">
         <v>65870</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837374</v>
+        <v>837258</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1954048</v>
+        <v>1956523</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844142</v>
+        <v>844020</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1967345</v>
+        <v>1964748</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848407</v>
+        <v>848284</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1982981</v>
+        <v>1981590</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>844766</v>
+        <v>844652</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1962152</v>
+        <v>1956912</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>815775</v>
+        <v>815660</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947337</v>
+        <v>1943110</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>826969</v>
+        <v>826844</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1928179</v>
+        <v>1932741</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>836891</v>
+        <v>836775</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1954540</v>
+        <v>1951967</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624863</v>
+        <v>624735</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>300733</v>
+        <v>296512</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>623155</v>
+        <v>623070</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>286918</v>
+        <v>290770</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624241</v>
+        <v>624141</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>276744</v>
+        <v>282399</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>835949</v>
+        <v>835834</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1951625</v>
+        <v>1953536</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>815817</v>
+        <v>815847</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1948754</v>
+        <v>1948140</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>838848</v>
+        <v>838865</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1954799</v>
+        <v>1955192</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3254516</v>
+        <v>3254251</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1063789</v>
+        <v>1063524</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2 registrados para Agosto 2026</t>
+          <t>1 registrados para Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4788,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -4822,34 +4822,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>infraplus</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus</t>
+          <t>Tivio Banks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>carteira</t>
+          <t>números no comentário</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
+          <t>o texto cita 10,54% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>alt180</t>
+          <t>banks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tivio ALT 180</t>
+          <t>Tivio Banks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4866,66 +4866,594 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alt90</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tivio ALT 90</t>
+          <t>Tivio Institucional</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>comentário</t>
+          <t>números no comentário</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+          <t>o texto cita 10,44%, 95% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>institucional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Top Gestor Ações Long Only</t>
+          <t>Tivio Institucional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>% do benchmark (mes)</t>
+          <t>comentário</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>370% fora da faixa 0–300% — conferir unidade ou sinal do benchmark</t>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>o texto cita 10,73% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>inst15</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>o texto cita 10,65% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>inst30</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tivio Institucional 30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>carteira</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>o texto cita 7,05% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>infraplus</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bvp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tivio BVP</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>o texto cita 10,55% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bvp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tivio BVP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>rfcp</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tivio RF CP</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>o texto cita 93% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>rfcp</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tivio RF CP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>o texto cita 26,79%, 34,87% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>o texto cita 19,70% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>alt90</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>o texto cita 19,70% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>altlight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>topgestorlongonly</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Top Gestor Ações Long Only</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>% do benchmark (mes)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>370% fora da faixa 0–300% — conferir unidade ou sinal do benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>infrapluscdi</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>o texto cita 8,64%, 82% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>infrapluscdi</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>esplanada</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Tivio Esplanada</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>carteira</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>esplanada</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>o texto cita 7,17% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>esplanada</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>números no comentário</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>o texto cita 10,03% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>legacy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>comentário</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
         </is>
       </c>
     </row>
@@ -4940,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4974,12 +5502,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>altlight</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tivio ALT Light</t>
+          <t>BV Top Gestor Crédito Privado</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4996,12 +5524,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Top Gestor Crédito Privado</t>
+          <t>Tivio Top Gestor HY</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5018,12 +5546,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tivio Top Gestor HY</t>
+          <t>BV Top Gestor RF Ativo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5040,56 +5568,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestormacro</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Top Gestor RF Ativo</t>
+          <t>BV Top Gestor Macro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>comentário do gestor</t>
+          <t>rentabilidade</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>não preenchido no arquivo de comentários</t>
+          <t>sem cotas na dados_mensais</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>topgestormacro</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Top Gestor Macro</t>
+          <t>Top Gestor Ações Long Only</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rentabilidade</t>
+          <t>comentário do gestor</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sem cotas na dados_mensais</t>
+          <t>não preenchido no arquivo de comentários</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Top Gestor Ações Long Only</t>
+          <t>Tivio Top Manager Global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5106,12 +5634,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tivio Top Manager Global</t>
+          <t>Tivio RF Ativo Longo Prazo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5128,12 +5656,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>prevlowvol</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tivio RF Ativo Longo Prazo</t>
+          <t>Tivio Prev Low Vol Itaú</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5150,42 +5678,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>atuarial</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tivio Prev Low Vol Itaú</t>
+          <t>Tivio Atuarial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>comentário do gestor</t>
+          <t>rentabilidade</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>não preenchido no arquivo de comentários</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>atuarial</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tivio Atuarial</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rentabilidade</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>sem cotas na dados_mensais</t>
         </is>
@@ -11266,7 +11772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -11362,100 +11868,49 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>relatorio/bvp</t>
+          <t>tivio-email-fundos-credito.html</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>bvp</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
+          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>relatorio/atuarial</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>atuarial</t>
+          <t>topgestormacro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>relatório não gerado: sem dados nesta edição</t>
+          <t>sem dados — rentabilidade e PL mantidos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>relatorio/credito_privado</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bvp</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
-        <is>
-          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>tivio-email-fundos-credito.html</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>alt180</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>tivio-post-investment-solutions.html</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>topgestormacro</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>sem dados — rentabilidade e PL mantidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>card "Gerador de Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
         </is>
@@ -11472,7 +11927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11500,7 +11955,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11509,531 +11964,156 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837258</v>
+        <v>840762</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1956523</v>
+        <v>814983</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Relatório de Gestão - Crédito Privado - Agosto 2026.html</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844020</v>
+        <v>719736</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-construtor-one-pager.html</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1964748</v>
+        <v>88026</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-email-fundos-credito.html</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848284</v>
+        <v>176798</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-email-nordea-studio.html</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1981590</v>
+        <v>50469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-post-credito-estruturado.html</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>844652</v>
+        <v>114702</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-post-credito-privado.html</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1956912</v>
+        <v>127504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>tivio-post-investment-solutions.html</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>815660</v>
+        <v>105529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pptx</t>
+          <t>tivio-central.html</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>pptx</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1943110</v>
+        <v>65182</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>index.html</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>826844</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>1932741</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>836775</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1951967</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>624735</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>296512</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>623070</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>290770</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>624141</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>282399</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>835834</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1953536</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>815847</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1948140</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>pdf</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>838865</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pptx</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pptx</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1955192</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Relatório de Gestão - Crédito Privado - Agosto 2026.html</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>3254251</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Relatório de Gestão - Crédito Estruturado - Agosto 2026.html</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1063524</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>tivio-construtor-one-pager.html</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>88026</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>tivio-email-fundos-credito.html</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>176798</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>tivio-email-nordea-studio.html</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>50469</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>tivio-post-credito-estruturado.html</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>114702</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tivio-post-credito-privado.html</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>127504</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>tivio-post-investment-solutions.html</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>105529</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>tivio-central.html</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>65870</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>index.html</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>html</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
         <v>390</v>
       </c>
     </row>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>1 registrados para Agosto 2026</t>
+          <t>2 registrados para Agosto 2026</t>
         </is>
       </c>
     </row>
@@ -4788,12 +4788,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="58" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -4822,34 +4822,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>infraplus</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tivio Banks</t>
+          <t>Tivio Infra Plus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>números no comentário</t>
+          <t>carteira</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>o texto cita 10,54% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+          <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>banks</t>
+          <t>alt180</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tivio Banks</t>
+          <t>Tivio ALT 180</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4866,594 +4866,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>alt90</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tivio Institucional</t>
+          <t>Tivio ALT 90</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>números no comentário</t>
+          <t>comentário</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>o texto cita 10,44%, 95% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
+          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>institucional</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tivio Institucional</t>
+          <t>Top Gestor Ações Long Only</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>comentário</t>
+          <t>% do benchmark (mes)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
+          <t>370% fora da faixa 0–300% — conferir unidade ou sinal do benchmark</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inst15</t>
+          <t>esplanada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tivio Institucional 15</t>
+          <t>Tivio Esplanada</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>números no comentário</t>
+          <t>carteira</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>o texto cita 10,73% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>inst15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tivio Institucional 15</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Tivio Institucional 30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>o texto cita 10,65% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>inst30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Tivio Institucional 30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>carteira</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>o texto cita 7,05% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>infraplus</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>bvp</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tivio BVP</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>o texto cita 10,55% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>bvp</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Tivio BVP</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>rfcp</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tivio RF CP</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>o texto cita 93% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rfcp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tivio RF CP</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>alt180</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Tivio ALT 180</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>o texto cita 26,79%, 34,87% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>alt180</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tivio ALT 180</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>alt90</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Tivio ALT 90</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>o texto cita 19,70% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>alt90</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Tivio ALT 90</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>altlight</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tivio ALT Light</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>o texto cita 19,70% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>altlight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Tivio ALT Light</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>topgestorlongonly</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Top Gestor Ações Long Only</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>% do benchmark (mes)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>370% fora da faixa 0–300% — conferir unidade ou sinal do benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>infrapluscdi</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus CDI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>o texto cita 8,64%, 82% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>infrapluscdi</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Tivio Infra Plus CDI</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>esplanada</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>carteira</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>linhas sem data na Base Carteira — a alocação exibida pode ser de outro mês; conferir a coluna Data da planilha</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>esplanada</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>o texto cita 7,17% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>esplanada</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Tivio Esplanada</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>legacy</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>números no comentário</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>o texto cita 10,03% — nenhum bate com um valor calculado deste fundo nesta edição. Conferir se o texto é do mês certo (o sistema não altera o texto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>legacy</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Tivio Legacy Prev</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>comentário</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>o texto se refere a "setembro" como o mês corrente — a data base é agosto/2026. Conferir se o comentário é o desta edição.</t>
         </is>
       </c>
     </row>
@@ -5468,7 +4940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5502,12 +4974,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>topgestor</t>
+          <t>altlight</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Top Gestor Crédito Privado</t>
+          <t>Tivio ALT Light</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5524,12 +4996,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>topgestorhy</t>
+          <t>topgestor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tivio Top Gestor HY</t>
+          <t>BV Top Gestor Crédito Privado</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5546,12 +5018,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>topgestorativo</t>
+          <t>topgestorhy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Top Gestor RF Ativo</t>
+          <t>Tivio Top Gestor HY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5568,56 +5040,56 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>topgestormacro</t>
+          <t>topgestorativo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Top Gestor Macro</t>
+          <t>BV Top Gestor RF Ativo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rentabilidade</t>
+          <t>comentário do gestor</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>sem cotas na dados_mensais</t>
+          <t>não preenchido no arquivo de comentários</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>topgestorlongonly</t>
+          <t>topgestormacro</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Top Gestor Ações Long Only</t>
+          <t>BV Top Gestor Macro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>comentário do gestor</t>
+          <t>rentabilidade</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>não preenchido no arquivo de comentários</t>
+          <t>sem cotas na dados_mensais</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>topmanagerglobal</t>
+          <t>topgestorlongonly</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tivio Top Manager Global</t>
+          <t>Top Gestor Ações Long Only</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5634,12 +5106,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ativorf</t>
+          <t>topmanagerglobal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tivio RF Ativo Longo Prazo</t>
+          <t>Tivio Top Manager Global</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5656,12 +5128,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>prevlowvol</t>
+          <t>ativorf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tivio Prev Low Vol Itaú</t>
+          <t>Tivio RF Ativo Longo Prazo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5678,20 +5150,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>prevlowvol</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tivio Prev Low Vol Itaú</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>comentário do gestor</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>não preenchido no arquivo de comentários</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>atuarial</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Tivio Atuarial</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>rentabilidade</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>sem cotas na dados_mensais</t>
         </is>
@@ -11772,7 +11266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -11868,49 +11362,100 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tivio-email-fundos-credito.html</t>
+          <t>relatorio/bvp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>alt180</t>
+          <t>bvp</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
+          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>relatorio/atuarial</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>topgestormacro</t>
+          <t>atuarial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sem dados — rentabilidade e PL mantidos</t>
+          <t>relatório não gerado: sem dados nesta edição</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>relatorio/credito_privado</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>bvp</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>logo não encontrado em assets/logos (procurei "tivio_bvp")</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>alt180</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>o texto se refere a "julho" como o mês corrente — a data base é agosto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>topgestormacro</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sem dados — rentabilidade e PL mantidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>tivio-central.html</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>tivio-central.html</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>card "Gerador de Relatório de Gestão · Incentivado CDI 30" removido: aponta para "Tivio Incentivado CDI 30 - Relatório de Gestão Mensal.html", que não existe nesta edição</t>
         </is>
@@ -11927,7 +11472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11955,7 +11500,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11964,156 +11509,531 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>840762</v>
+        <v>837689</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
+          <t>Tivio Banks - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>814983</v>
+        <v>1962279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Relatório de Gestão - Crédito Privado - Agosto 2026.html</t>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>719736</v>
+        <v>844461</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tivio-construtor-one-pager.html</t>
+          <t>Tivio Institucional - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88026</v>
+        <v>1969668</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tivio-email-fundos-credito.html</t>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>176798</v>
+        <v>848724</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tivio-email-nordea-studio.html</t>
+          <t>Tivio Institucional 15 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>50469</v>
+        <v>1987504</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tivio-post-credito-estruturado.html</t>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>114702</v>
+        <v>845108</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tivio-post-credito-privado.html</t>
+          <t>Tivio Institucional 30 - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>127504</v>
+        <v>1963344</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tivio-post-investment-solutions.html</t>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>105529</v>
+        <v>816001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tivio-central.html</t>
+          <t>Tivio Infra Plus - Relatório de Gestão - Agosto 2026.pptx</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>pptx</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>65182</v>
+        <v>1947425</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>827327</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tivio BVP - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1942080</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>837221</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tivio RF CP - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1959817</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>624550</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Tivio ALT 180 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>296383</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>622922</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tivio ALT 90 - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>290733</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>624149</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Tivio ALT Light - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>282447</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>836306</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tivio Infra Plus CDI - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1959835</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>816045</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Tivio Esplanada - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1952312</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>839195</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Tivio Legacy Prev - Relatório de Gestão - Agosto 2026.pptx</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>pptx</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1962176</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Relatório de Gestão - Crédito Privado - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3256183</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Relatório de Gestão - Crédito Estruturado - Agosto 2026.html</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1064610</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tivio-construtor-one-pager.html</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>88026</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tivio-email-fundos-credito.html</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>176798</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tivio-email-nordea-studio.html</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>50469</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-estruturado.html</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>114702</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tivio-post-credito-privado.html</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>127504</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tivio-post-investment-solutions.html</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>105529</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>tivio-central.html</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>65870</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>index.html</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>html</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C37" t="n">
         <v>390</v>
       </c>
     </row>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837689</v>
+        <v>837819</v>
       </c>
     </row>
     <row r="3">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844461</v>
+        <v>844468</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969668</v>
+        <v>1969672</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848724</v>
+        <v>848655</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1987504</v>
+        <v>1987498</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>845108</v>
+        <v>845128</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1963344</v>
+        <v>1963705</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>816001</v>
+        <v>816180</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947425</v>
+        <v>1947270</v>
       </c>
     </row>
     <row r="12">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>837221</v>
+        <v>837261</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1959817</v>
+        <v>1959832</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624550</v>
+        <v>624721</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296383</v>
+        <v>296512</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>622922</v>
+        <v>623060</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290733</v>
+        <v>290770</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624149</v>
+        <v>624139</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282447</v>
+        <v>282399</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836306</v>
+        <v>836366</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959835</v>
+        <v>1959857</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>816045</v>
+        <v>816368</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1952312</v>
+        <v>1952568</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>839195</v>
+        <v>839489</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1962176</v>
+        <v>1960320</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3256183</v>
+        <v>3256574</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1064610</v>
+        <v>1064688</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837819</v>
+        <v>837841</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1962279</v>
+        <v>1962211</v>
       </c>
     </row>
     <row r="4">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296512</v>
+        <v>296383</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>623060</v>
+        <v>622912</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290770</v>
+        <v>290733</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624139</v>
+        <v>624147</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282399</v>
+        <v>282447</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836366</v>
+        <v>836369</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959857</v>
+        <v>1959851</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>816368</v>
+        <v>816222</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1952568</v>
+        <v>1952396</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>839489</v>
+        <v>839350</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1960320</v>
+        <v>1960537</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3256574</v>
+        <v>3256752</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1064688</v>
+        <v>1064858</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296383</v>
+        <v>296512</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>622912</v>
+        <v>623060</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290733</v>
+        <v>290770</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624147</v>
+        <v>624139</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282447</v>
+        <v>282399</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836369</v>
+        <v>836366</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959851</v>
+        <v>1959857</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>816222</v>
+        <v>838809</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1952396</v>
+        <v>1968601</v>
       </c>
     </row>
     <row r="26">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3256752</v>
+        <v>3258241</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1064858</v>
+        <v>1065251</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11472,7 +11472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969672</v>
+        <v>1969569</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848655</v>
+        <v>848514</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1987498</v>
+        <v>1987494</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>845128</v>
+        <v>844982</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1963705</v>
+        <v>1963839</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>816180</v>
+        <v>816073</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947270</v>
+        <v>1947306</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>827327</v>
+        <v>827186</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1942080</v>
+        <v>1942156</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>837261</v>
+        <v>837128</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1959832</v>
+        <v>1959089</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624721</v>
+        <v>624536</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296512</v>
+        <v>296383</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>623060</v>
+        <v>622912</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290770</v>
+        <v>290733</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624139</v>
+        <v>624147</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282399</v>
+        <v>282447</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836366</v>
+        <v>836369</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959857</v>
+        <v>1959851</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>838809</v>
+        <v>838521</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1968601</v>
+        <v>1968814</v>
       </c>
     </row>
     <row r="26">
@@ -12025,15 +12025,45 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>destaques</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>emails</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>png</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4096</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>index.html</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>html</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C39" t="n">
         <v>390</v>
       </c>
     </row>

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837841</v>
+        <v>837852</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1962211</v>
+        <v>1962146</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844468</v>
+        <v>844475</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969569</v>
+        <v>1969655</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848514</v>
+        <v>848666</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1987494</v>
+        <v>1987683</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>844982</v>
+        <v>845139</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1963839</v>
+        <v>1963695</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>816073</v>
+        <v>816194</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947306</v>
+        <v>1947219</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>827186</v>
+        <v>827340</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1942156</v>
+        <v>1942019</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>837128</v>
+        <v>837278</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1959089</v>
+        <v>1959870</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624536</v>
+        <v>624730</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296383</v>
+        <v>296504</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>622912</v>
+        <v>623076</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290733</v>
+        <v>290714</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624147</v>
+        <v>624156</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282447</v>
+        <v>282324</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836369</v>
+        <v>836377</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959851</v>
+        <v>1959922</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>838521</v>
+        <v>838819</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1968814</v>
+        <v>1968614</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>839350</v>
+        <v>839500</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1960537</v>
+        <v>1960279</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3258241</v>
+        <v>3258333</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1065251</v>
+        <v>1065343</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837852</v>
+        <v>837832</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1962146</v>
+        <v>1962136</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844475</v>
+        <v>844455</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969655</v>
+        <v>1969646</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848666</v>
+        <v>848644</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1987683</v>
+        <v>1987673</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>845139</v>
+        <v>845141</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1963695</v>
+        <v>1963689</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>816194</v>
+        <v>816089</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947219</v>
+        <v>1947249</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>827340</v>
+        <v>827201</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1942019</v>
+        <v>1942090</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>837278</v>
+        <v>837147</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1959870</v>
+        <v>1959121</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624730</v>
+        <v>624532</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296504</v>
+        <v>296368</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>623076</v>
+        <v>622912</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290714</v>
+        <v>290671</v>
       </c>
     </row>
     <row r="20">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282324</v>
+        <v>282366</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836377</v>
+        <v>836383</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959922</v>
+        <v>1959909</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>838819</v>
+        <v>838535</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1968614</v>
+        <v>1968819</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>839500</v>
+        <v>839366</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1960279</v>
+        <v>1960489</v>
       </c>
     </row>
     <row r="28">
@@ -11929,7 +11929,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>88026</v>
+        <v>88025</v>
       </c>
     </row>
     <row r="31">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>837832</v>
+        <v>832380</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1962136</v>
+        <v>1961068</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>844455</v>
+        <v>839113</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1969646</v>
+        <v>1968576</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>848644</v>
+        <v>843397</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1987673</v>
+        <v>1986603</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>845141</v>
+        <v>839298</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1963689</v>
+        <v>1962582</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>816089</v>
+        <v>810307</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1947249</v>
+        <v>1946106</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>827201</v>
+        <v>821525</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1942090</v>
+        <v>1940905</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>837147</v>
+        <v>831499</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1959121</v>
+        <v>1958756</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>624532</v>
+        <v>618635</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>296368</v>
+        <v>295387</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>622912</v>
+        <v>616882</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>290671</v>
+        <v>289597</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>624156</v>
+        <v>617948</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>282366</v>
+        <v>281206</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>836383</v>
+        <v>830443</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1959909</v>
+        <v>1958809</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>838535</v>
+        <v>832990</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1968819</v>
+        <v>1967496</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>839366</v>
+        <v>833734</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1960489</v>
+        <v>1959166</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3258333</v>
+        <v>3231313</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1065343</v>
+        <v>1057237</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11241,7 +11241,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0,00% a.a.</t>
+          <t>0,50% a.a.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>832380</v>
+        <v>832189</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1961068</v>
+        <v>1961063</v>
       </c>
     </row>
     <row r="4">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>839113</v>
+        <v>838925</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1968576</v>
+        <v>1968568</v>
       </c>
     </row>
     <row r="6">
@@ -11569,7 +11569,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>843397</v>
+        <v>843208</v>
       </c>
     </row>
     <row r="7">
@@ -11584,7 +11584,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1986603</v>
+        <v>1986595</v>
       </c>
     </row>
     <row r="8">
@@ -11599,7 +11599,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>839298</v>
+        <v>839119</v>
       </c>
     </row>
     <row r="9">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1962582</v>
+        <v>1962573</v>
       </c>
     </row>
     <row r="10">
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>810307</v>
+        <v>810134</v>
       </c>
     </row>
     <row r="11">
@@ -11644,7 +11644,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1946106</v>
+        <v>1946096</v>
       </c>
     </row>
     <row r="12">
@@ -11659,7 +11659,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>821525</v>
+        <v>821345</v>
       </c>
     </row>
     <row r="13">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1940905</v>
+        <v>1940895</v>
       </c>
     </row>
     <row r="14">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>831499</v>
+        <v>831185</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1958756</v>
+        <v>1958003</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>618635</v>
+        <v>618261</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>295387</v>
+        <v>295251</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>616882</v>
+        <v>616542</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>289597</v>
+        <v>289552</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617948</v>
+        <v>617774</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281206</v>
+        <v>281246</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>830443</v>
+        <v>830272</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1958809</v>
+        <v>1958793</v>
       </c>
     </row>
     <row r="24">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>832990</v>
+        <v>832511</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1967496</v>
+        <v>1967697</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>833734</v>
+        <v>833420</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1959166</v>
+        <v>1959374</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3231313</v>
+        <v>3231558</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1057237</v>
+        <v>1057482</v>
       </c>
     </row>
     <row r="30">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 46.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 27.0}, {'n': 'Bancário', 'p': 6.1}, {'n': 'Fiagro', 'p': 5.5}, {'n': 'Liquidez', 'p': 5.3}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Precatório', 'p': 2.7}, {'n': 'Crédito Estruturado', 'p': 2.6}]</t>
+          <t>[{'n': 'FIDC Sênior', 'p': 46.3}, {'n': 'FIDC Mezanino', 'p': 27.0}, {'n': 'Liquidez', 'p': 11.4}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Fiagro', 'p': 3.2}, {'n': 'Precatórios', 'p': 2.7}]</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDCs Cotas Sênior', 'p': 82.9}, {'n': 'Bancário', 'p': 8.3}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Fiagro', 'p': 2.9}, {'n': 'Liquidez', 'p': 1.9}, {'n': 'FIDCs Cotas Mezanino', 'p': 0.6}]</t>
+          <t>[{'n': 'FIDC Sênior', 'p': 81.4}, {'n': 'Liquidez', 'p': 10.2}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.9}, {'n': 'Fiagro', 'p': 1.5}, {'n': 'FIDC Mezanino', 'p': 0.6}]</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cotas Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'Ações', 'p': 1.9}]</t>
+          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDC Sênior', 'p': 23.6}, {'n': 'Liquidez', 'p': 7.7}, {'n': 'Padrão', 'p': 2.0}]</t>
         </is>
       </c>
     </row>
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1968568</v>
+        <v>1968465</v>
       </c>
     </row>
     <row r="6">
@@ -11689,7 +11689,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>831185</v>
+        <v>831318</v>
       </c>
     </row>
     <row r="15">
@@ -11704,7 +11704,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1958003</v>
+        <v>1958746</v>
       </c>
     </row>
     <row r="16">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>618261</v>
+        <v>618455</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>295251</v>
+        <v>295342</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>616542</v>
+        <v>616972</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>289552</v>
+        <v>289721</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617774</v>
+        <v>617607</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281246</v>
+        <v>281173</v>
       </c>
     </row>
     <row r="22">
@@ -11809,7 +11809,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>830272</v>
+        <v>830269</v>
       </c>
     </row>
     <row r="23">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1958793</v>
+        <v>1958799</v>
       </c>
     </row>
     <row r="24">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1057482</v>
+        <v>1057406</v>
       </c>
     </row>
     <row r="30">
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>114702</v>
+        <v>114655</v>
       </c>
     </row>
     <row r="34">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -1483,7 +1483,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDC Sênior', 'p': 46.3}, {'n': 'FIDC Mezanino', 'p': 27.0}, {'n': 'Liquidez', 'p': 11.4}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Fiagro', 'p': 3.2}, {'n': 'Precatórios', 'p': 2.7}]</t>
+          <t>[{'n': 'FIDCs Cota Sênior', 'p': 46.3}, {'n': 'FIDCs Cota Mezanino', 'p': 27.0}, {'n': 'Liquidez', 'p': 11.4}, {'n': 'Crédito Estruturado', 'p': 5.5}, {'n': 'Crédito Privado', 'p': 3.4}, {'n': 'Fiagro', 'p': 3.2}, {'n': 'Precatório', 'p': 2.7}]</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>[{'n': 'FIDC Sênior', 'p': 81.4}, {'n': 'Liquidez', 'p': 10.2}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.9}, {'n': 'Fiagro', 'p': 1.5}, {'n': 'FIDC Mezanino', 'p': 0.6}]</t>
+          <t>[{'n': 'FIDCs Cota Sênior', 'p': 81.4}, {'n': 'Liquidez', 'p': 10.2}, {'n': 'Crédito Privado', 'p': 3.6}, {'n': 'Crédito Estruturado', 'p': 2.9}, {'n': 'Fiagro', 'p': 1.5}, {'n': 'FIDCs Cota Mezanino', 'p': 0.6}]</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDC Sênior', 'p': 23.6}, {'n': 'Liquidez', 'p': 7.7}, {'n': 'Padrão', 'p': 2.0}]</t>
+          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cota Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>832189</v>
+        <v>832315</v>
       </c>
     </row>
     <row r="3">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>838925</v>
+        <v>838802</v>
       </c>
     </row>
     <row r="5">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1968465</v>
+        <v>1968568</v>
       </c>
     </row>
     <row r="6">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>618455</v>
+        <v>618536</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>295342</v>
+        <v>295318</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>616972</v>
+        <v>616870</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>289721</v>
+        <v>289653</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617607</v>
+        <v>617753</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281173</v>
+        <v>281200</v>
       </c>
     </row>
     <row r="22">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>832511</v>
+        <v>832799</v>
       </c>
     </row>
     <row r="25">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1967697</v>
+        <v>1967484</v>
       </c>
     </row>
     <row r="26">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>833420</v>
+        <v>833559</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1959374</v>
+        <v>1959157</v>
       </c>
     </row>
     <row r="28">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1057406</v>
+        <v>1057479</v>
       </c>
     </row>
     <row r="30">
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>114655</v>
+        <v>114680</v>
       </c>
     </row>
     <row r="34">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Crédito Privado', 'p': 25.8}, {'n': 'FIDCs Cota Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
+          <t>[{'n': 'Bancário', 'p': 40.7}, {'n': 'Debêntures', 'p': 25.8}, {'n': 'FIDCs Cota Sênior', 'p': 23.5}, {'n': 'Liquidez', 'p': 7.8}, {'n': 'FIP', 'p': 1.9}]</t>
         </is>
       </c>
     </row>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>832315</v>
+        <v>832189</v>
       </c>
     </row>
     <row r="3">
@@ -11539,7 +11539,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>838802</v>
+        <v>838925</v>
       </c>
     </row>
     <row r="5">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617753</v>
+        <v>617677</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281200</v>
+        <v>281152</v>
       </c>
     </row>
     <row r="22">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1958799</v>
+        <v>1958793</v>
       </c>
     </row>
     <row r="24">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1057479</v>
+        <v>1057454</v>
       </c>
     </row>
     <row r="30">
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>114680</v>
+        <v>114675</v>
       </c>
     </row>
     <row r="34">

--- a/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
+++ b/AutomaTivio/saida/2026-08/conferencia_2026-08.xlsx
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>832189</v>
+        <v>832291</v>
       </c>
     </row>
     <row r="3">
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1961063</v>
+        <v>1961067</v>
       </c>
     </row>
     <row r="4">
@@ -11719,7 +11719,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>618536</v>
+        <v>618543</v>
       </c>
     </row>
     <row r="17">
@@ -11734,7 +11734,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>295318</v>
+        <v>295317</v>
       </c>
     </row>
     <row r="18">
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>616870</v>
+        <v>617077</v>
       </c>
     </row>
     <row r="19">
@@ -11764,7 +11764,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>289653</v>
+        <v>289794</v>
       </c>
     </row>
     <row r="20">
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>617677</v>
+        <v>617709</v>
       </c>
     </row>
     <row r="21">
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>281152</v>
+        <v>281192</v>
       </c>
     </row>
     <row r="22">
@@ -11824,7 +11824,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1958793</v>
+        <v>1958799</v>
       </c>
     </row>
     <row r="24">
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>833559</v>
+        <v>833617</v>
       </c>
     </row>
     <row r="27">
@@ -11884,7 +11884,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1959157</v>
+        <v>1959162</v>
       </c>
     </row>
     <row r="28">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3231558</v>
+        <v>3231856</v>
       </c>
     </row>
     <row r="29">
@@ -11914,7 +11914,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1057454</v>
+        <v>1057746</v>
       </c>
     </row>
     <row r="30">
